--- a/agrra_monitoring/data_raw/ATG_NEMMA_2025/Raw/Metadata.xlsx
+++ b/agrra_monitoring/data_raw/ATG_NEMMA_2025/Raw/Metadata.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\ATG\Raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AGRRA Group Work\Data Product Fix\Ruleo\NEMMA&amp;CadesReef2025\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59666A5-9F43-4809-96CC-373EB242EFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17DC61A-12D6-49F4-9C99-D9C4B4BCC8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TermsOfUse" sheetId="8" r:id="rId1"/>
+    <sheet name="TermsOfUse" sheetId="9" r:id="rId1"/>
     <sheet name="Batch" sheetId="1" r:id="rId2"/>
     <sheet name="Survey" sheetId="2" r:id="rId3"/>
     <sheet name="Transect" sheetId="3" r:id="rId4"/>
@@ -22,7 +22,7 @@
     <sheet name="CoralTaxonomy" sheetId="6" r:id="rId7"/>
     <sheet name="FishTaxonomy" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -2144,48 +2144,39 @@
     <t>Diadema Predator</t>
   </si>
   <si>
-    <t>Created: 2025 May 29</t>
-  </si>
-  <si>
-    <t>Version 1.0</t>
-  </si>
-  <si>
+    <t>Created: 2026 May 29</t>
+  </si>
+  <si>
+    <t>AGRRA Terms of Data Service</t>
+  </si>
+  <si>
+    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae, and fishes, and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA’s goal is to provide data contributors access to the AGRRA data platform, which provides: 
+a)	a standardized way to enter coral reef monitoring data with built in quality controls,
+b)	an efficient way to process data and visualize data through interactive graphics,
+c)	synthesized data products provided as RAW data and Calculated Products, and 
+d)	a centralized and secure place to manage and store data.
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="13"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Date produced: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data in this country batch were produced in collaboration with the batch owner: Margaret Wilson. These data products are in draft form and are under review. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Data License below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use. </t>
-    </r>
-  </si>
-  <si>
-    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae and fishes and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conditions of Use of AGRRA Data Products
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">In order to use the AGRRA dataset, you need to accept the Terms and Conditions in the AGRRA Data License below.
-</t>
+      <t xml:space="preserve">
+1. Ownership &amp; Intellectual Property</t>
     </r>
     <r>
       <rPr>
@@ -2196,17 +2187,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>AGRRA Data License and Data Use Agreements</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
       <t xml:space="preserve">
-By accessing and using any of the datasets distributed by AGRRA, you acknowledge that you have read, understood, and agree to comply with the terms and conditions contained within this agreement. A Data Use Agreement (DUA) must be entered into before there is any use or distribution of a data set to an outside entity. AGRRA may amend these terms and conditions at any time. Your continued use of this data constitutes acceptance of the terms and conditions stated at the time of your use. You should contact AGRRA to determine the current terms and conditions to which you are bound.
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
     </r>
     <r>
       <rPr>
@@ -2217,17 +2207,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Permissions and Proprietary Rights to Content</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-All datasets are the property of AGRRA and/or its affiliates, unless otherwise noted. With permission and DUA, you may use these datasets for non-commercial purposes, including research, education, presentations, and non-commercial publications. You understand and agree that you may not copy, reproduce, distribute or create derivative works for other purposes, without prior, written authorization from the AGRRA Project Leader. When using or publishing any parts of these datasets, proper acknowledgement of AGRRA and original source(s), is required.
-</t>
+      <t>Original Observations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The raw data collected during surveys remains the intellectual property of the original data collectors and their respective organizations.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2238,17 +2227,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Limitation of Liability</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-AGRRA makes reasonable efforts to provide accurate data and information through its website, database, and other channels. Nevertheless, you understand and agree that AGRRA shall not be liable for any loss or damage resulting from any use of, or inability to use, this data, or resulting from any errors or omissions in the data content.
-</t>
+      <t xml:space="preserve">Methodology &amp; Systems: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">All protocols (Benthic, Coral, Fish), platform systems, AGRRA content, and related tools remain the intellectual property of </t>
     </r>
     <r>
       <rPr>
@@ -2259,17 +2246,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Data Citation </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-For any use of AGRRA data or datasets managed by AGRRA, or for general reference to the project in peer-reviewed literature, use the citation specified in the data use policy or for general citation use the following format below to cite data retrieved from the AGRRA website or AGRRA database manager. 
-</t>
+      <t>Ocean Research &amp; Education Foundation, Inc. (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -2280,16 +2265,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Citation:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> AGRRA. 2024. Atlantic and Gulf Rapid Reef Assessment (AGRRA): An online database of AGRRA coral reef survey data. Available: http://agrra.org. (Accessed: Date [e.g., March 10, 2024]).
-</t>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, and their licensors, as applicable.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2300,19 +2285,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Acknowledgement:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> For general data, use: “We thank the following data providers: Atlantic Gulf Rapid Reef Assessment (AGRRA) contributors and data managers…”. Where noted, individual data contributors should be included in acknowledgments. 
-</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">Processed Metrics: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">The calculated metrics, custom-coded logic, and standardized protocols used to generate these spreadsheets are the proprietary property of </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2322,27 +2304,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Use Policy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Data collected under the auspices of AGRRA are available to the public after primary publication, or at most two years after the completion of the study unless proprietary restrictions are warranted. Request for the use of AGRRA data is to be made in writing and is subject to acceptance of the following conditions:
-1. The user agrees to provide valid name and contact information prior to requesting or downloading online data. This information will be used to ensure data agreements are in place, to contact the user in case of changes to the data, and may also be used by data set authors and AGRRA project administrators to document data usage.
-2. The user agrees to cite the data set author (if stated) and AGRRA in all publications in which the data are used, as per the instructions in “Data Citation”. 
-3. The user agrees to provide one copy of any manuscript based on AGRRA data to the AGRRA or data set author (if specified) prior to submitting it for peer-reviewed publication.
-4. The user also agrees to send one electronic copy or reports or publication (pdf format) to: data@agrra.org and gis@agrra.org. 
-5. Users are prohibited from selling or redistributing any data provided by AGRRA without explicit prior permission.
-6. If specified, users are to contact original investigators or data contributors responsible for data prior to data use, and where appropriate, are encouraged to consider collaboration and/or co-authorship with original investigators.
-7. Extensive efforts are made to ensure that data products are accurate and up to date, but the authors and AGRRA will not take responsibility for any errors that may exist in data provided. The user assumes all responsibility for errors in analysis or judgment resulting from use of the data.
-8. Any violation of the terms of this agreement will result in immediate forfeiture of the data and loss of access privileges to other AGRRA data sets.  </t>
-    </r>
-  </si>
-  <si>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2352,18 +2323,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Format of Data:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. Note these are draft data products from the beta version of the new AGRRA data portal (2024) and are currently in review. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
-    </r>
-  </si>
-  <si>
+      <t>Ocean Research &amp; Education Foundation (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.
+•	</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2373,6 +2343,601 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">User Content: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Users retain ownership of data, images, and other content they submit, but grant AGRRA the rights needed to store, process, share, and display that content in accordance with these terms.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Data Sharing &amp; Privacy Publication Protocol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA is committed to protecting the privacy of the Data Contributors with respect to their data batches and offers three privacy options for each data batch:
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Batch Privacy Options: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data Batches may be designated as Private, Public Summary, or Public. Some batch metadata may remain publicly visible to support transparency and attribution.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accounts &amp; Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors are responsible for their accounts, passwords, and all activity under their accounts, and must promptly report any suspected unauthorized access.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Permitted Uses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+•	Non-Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors and Third-party Users (with permission) are licensed to use these materials and datasets for research, education, conservation, and other non-commercial purposes.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Commercial use, sale, or redistribution of AGRRA materials, datasets, or API outputs requires prior written permission.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lawful and Responsible Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> All users must comply with applicable laws and must not misuse, disrupt, alter, scrape, or interfere with the platform, its software, security, or other users.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Citation &amp; Acknowledgment
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A. Guidance for Original Data Contributors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to cite your data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> When publishing, presenting, or otherwise sharing analyses based on your own contributed dataset, please cite the dataset using the suggested AGRRA format: [Surveyor Names/Organization], [Country] ([Year]). [Dataset Name/Region]. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, [Protocol Version Number] [Data Product Name]. [URL/DOI]. Accessed [Date].
+                o   Examples
+                         ▪For a specific survey: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smith, J. &amp; Reef Care Bahamas, Bahamas (2024). New Providence Benthic Surveys. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, v5.2 Coral &amp; Benthic Data. www.agrra.org. Accessed May 14, 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+                         ▪For an aggregated country-level report: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Belize Fisheries Department &amp; Healthy Reefs Initiative, Belize (2025). 2025 National Monitoring Data. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform. www.agrra.org. Accessed May 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In all publications and presentations using your contributed data, please acknowledge AGRRA as the platform that curates, manages, and provides access to the dataset.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suggested acknowledgment language:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "We acknowledge (or thank) the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Contributors are encouraged to remain available for collaboration when their expertise may strengthen data interpretation or publication.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notification of use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Please share an electronic copy of any final reports, publications, or presentations with AGRRA curated data to data@agrra.org.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B. Guidance for Third-Party Data Users</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Third-party users (not original data collectors) who would like to use an AGRRA data batch should first contact and obtain permission from the original data contributor and/or AGRRA at data@agrra.org. Once permission is granted, third-party users who utilize AGRRA-hosted data for research, presentations, reports, or publications shall give appropriate credit to both the original data contributors and AGRRA. The guidance below explains how to cite the original dataset and how to acknowledge AGRRA as the data platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">How to cite original data contributors: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Cite the dataset using the names of the original surveyors, organizations, country, year, and dataset title, following the AGRRA dataset citation format. AGRRA can provide guidance on the appropriate citation for the specific dataset used.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In addition to citing the original dataset, acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform as the system that curates, manages, and provides access to the data.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Suggested acknowledgment language: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">"We thank the original data contributors [insert surveyor and/or organization names, where available] and acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Direct contact and collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Third-party users are encouraged to contact the original data collectors to discuss collaboration or co-authorship, clarify interpretation, and share findings, where appropriate.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Liability &amp; Compliance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Integrity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA works diligently to maintain data accuracy; however, Data Contributors and Third-Party users are responsible for their own analyses, interpretations, and resulting conclusions.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No Warranty:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The platform, data, and related content are provided “as is” and “as available,” without guarantees of accuracy, availability, security, or fitness for a particular purpose.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limitation of Liability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA and its operators are not liable for indirect, incidental, consequential, or data-loss-related damages arising from the use of the platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Access Review: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">If these terms are not followed, AGRRA reserves the right to review, suspend, modify, or terminate access privileges or service availability as appropriate.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Changes &amp; Governing Law:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA may update these terms from time to time; continued use represents acceptance. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Metadata:</t>
     </r>
     <r>
@@ -2385,23 +2950,30 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
+    <t>Version 1.0</t>
+  </si>
+  <si>
+    <t>Data provided in these country batches were produced in collaboration with the batch owner: Ruleo Camacho. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Terms of Data Service below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-      </rPr>
-      <t>©</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ocean Research and Education Foundation</t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Format of Data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
     </r>
   </si>
 </sst>
@@ -2414,11 +2986,18 @@
     <numFmt numFmtId="165" formatCode="0.0000&quot;° N&quot;;0.0000&quot;° S&quot;;0.0000&quot;°&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0000&quot;° E&quot;;0.0000&quot;° W&quot;;0.0000&quot;°&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2442,16 +3021,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2474,7 +3072,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2488,6 +3086,66 @@
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2501,7 +3159,22 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2624,11 +3297,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2655,114 +3329,105 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{E361B8F9-EB77-47BB-A4BF-E5D74807B44F}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{8457A518-4F64-4BF8-8F2D-FD1153D63728}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{5B483864-18AB-4AE5-87AC-97B534A817EB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -2775,61 +3440,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322132</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBBF76A3-A89F-439E-A8D2-C1614BE3275F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6276976" y="180976"/>
-          <a:ext cx="2655756" cy="2038350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3118,1051 +3728,1601 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F91B84E0-3B88-451F-9925-8700B8E321B1}">
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69128EC-BDB1-4684-BB71-F6EDF1361C11}">
+  <dimension ref="A1:X70"/>
+  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="13" customWidth="1"/>
-    <col min="3" max="16384" width="9.7109375" style="13"/>
+    <col min="2" max="2" width="11.26953125" style="13" customWidth="1"/>
+    <col min="3" max="16384" width="9.7265625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>326</v>
       </c>
       <c r="B1" s="12"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="B2" s="12"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="18"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="21"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:23" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="24"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
         <v>329</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="17"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="27"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="30"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="30"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="30"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="30"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="30"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="30"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="30"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="30"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="30"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="30"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="30"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="30"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="30"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="30"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="30"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="30"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="30"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="30"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="30"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="30"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="30"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="30"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+      <c r="W33" s="30"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="30"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+      <c r="W35" s="30"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+      <c r="W36" s="30"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="30"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="30"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+      <c r="W39" s="30"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="30"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="28"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+      <c r="W41" s="30"/>
+      <c r="X41" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="21" t="s">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="28"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+      <c r="W42" s="30"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="28"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="30"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="28"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="29"/>
+      <c r="S44" s="29"/>
+      <c r="T44" s="29"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="29"/>
+      <c r="W44" s="30"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="28"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+      <c r="T45" s="29"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+      <c r="W45" s="30"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="28"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="30"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+      <c r="W47" s="30"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
+      <c r="W48" s="30"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="30"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" s="28"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
+      <c r="S50" s="29"/>
+      <c r="T50" s="29"/>
+      <c r="U50" s="29"/>
+      <c r="V50" s="29"/>
+      <c r="W50" s="30"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" s="28"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="29"/>
+      <c r="U51" s="29"/>
+      <c r="V51" s="29"/>
+      <c r="W51" s="30"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" s="28"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="30"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" s="28"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+      <c r="N53" s="29"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="29"/>
+      <c r="Q53" s="29"/>
+      <c r="R53" s="29"/>
+      <c r="S53" s="29"/>
+      <c r="T53" s="29"/>
+      <c r="U53" s="29"/>
+      <c r="V53" s="29"/>
+      <c r="W53" s="30"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
+      <c r="S54" s="29"/>
+      <c r="T54" s="29"/>
+      <c r="U54" s="29"/>
+      <c r="V54" s="29"/>
+      <c r="W54" s="30"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" s="28"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
+      <c r="W55" s="30"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" s="28"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29"/>
+      <c r="N56" s="29"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="29"/>
+      <c r="S56" s="29"/>
+      <c r="T56" s="29"/>
+      <c r="U56" s="29"/>
+      <c r="V56" s="29"/>
+      <c r="W56" s="30"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
+      <c r="U57" s="29"/>
+      <c r="V57" s="29"/>
+      <c r="W57" s="30"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" s="28"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="30"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" s="28"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="29"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="29"/>
+      <c r="P59" s="29"/>
+      <c r="Q59" s="29"/>
+      <c r="R59" s="29"/>
+      <c r="S59" s="29"/>
+      <c r="T59" s="29"/>
+      <c r="U59" s="29"/>
+      <c r="V59" s="29"/>
+      <c r="W59" s="30"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+      <c r="T60" s="29"/>
+      <c r="U60" s="29"/>
+      <c r="V60" s="29"/>
+      <c r="W60" s="30"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" s="28"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="30"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" s="28"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="29"/>
+      <c r="P62" s="29"/>
+      <c r="Q62" s="29"/>
+      <c r="R62" s="29"/>
+      <c r="S62" s="29"/>
+      <c r="T62" s="29"/>
+      <c r="U62" s="29"/>
+      <c r="V62" s="29"/>
+      <c r="W62" s="30"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="31"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
+      <c r="M63" s="32"/>
+      <c r="N63" s="32"/>
+      <c r="O63" s="32"/>
+      <c r="P63" s="32"/>
+      <c r="Q63" s="32"/>
+      <c r="R63" s="32"/>
+      <c r="S63" s="32"/>
+      <c r="T63" s="32"/>
+      <c r="U63" s="32"/>
+      <c r="V63" s="32"/>
+      <c r="W63" s="33"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="34"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="36"/>
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
+      <c r="V65" s="36"/>
+      <c r="W65" s="37"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="38"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
+      <c r="Q66" s="39"/>
+      <c r="R66" s="39"/>
+      <c r="S66" s="39"/>
+      <c r="T66" s="39"/>
+      <c r="U66" s="39"/>
+      <c r="V66" s="39"/>
+      <c r="W66" s="40"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="41" t="s">
         <v>331</v>
       </c>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="23"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="29"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="29"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="29"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
-      <c r="V21" s="28"/>
-      <c r="W21" s="29"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="29"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="29"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="29"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="29"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="29"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="29"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="29"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="29"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="28"/>
-      <c r="V30" s="28"/>
-      <c r="W30" s="29"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="29"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="29"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="29"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="29"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="29"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="29"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="29"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="29"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="29"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="29"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="28"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="29"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="29"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="29"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="28"/>
-      <c r="T44" s="28"/>
-      <c r="U44" s="28"/>
-      <c r="V44" s="28"/>
-      <c r="W44" s="29"/>
-    </row>
-    <row r="45" spans="1:23" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="28"/>
-      <c r="S45" s="28"/>
-      <c r="T45" s="28"/>
-      <c r="U45" s="28"/>
-      <c r="V45" s="28"/>
-      <c r="W45" s="29"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="29"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="34"/>
-      <c r="T47" s="34"/>
-      <c r="U47" s="34"/>
-      <c r="V47" s="34"/>
-      <c r="W47" s="35"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
-      <c r="K48" s="37"/>
-      <c r="L48" s="37"/>
-      <c r="M48" s="37"/>
-      <c r="N48" s="37"/>
-      <c r="O48" s="37"/>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="37"/>
-      <c r="R48" s="37"/>
-      <c r="S48" s="37"/>
-      <c r="T48" s="37"/>
-      <c r="U48" s="37"/>
-      <c r="V48" s="37"/>
-      <c r="W48" s="38"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="40"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="40"/>
-      <c r="T49" s="40"/>
-      <c r="U49" s="40"/>
-      <c r="V49" s="40"/>
-      <c r="W49" s="41"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="43"/>
-      <c r="P50" s="43"/>
-      <c r="Q50" s="43"/>
-      <c r="R50" s="43"/>
-      <c r="S50" s="43"/>
-      <c r="T50" s="43"/>
-      <c r="U50" s="43"/>
-      <c r="V50" s="43"/>
-      <c r="W50" s="44"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S51" s="45" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="46"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="47"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="47"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="47"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="47"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="47"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="47"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="47"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="47"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="47"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="47"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="47"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="47"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="47"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="47"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="47"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="47"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="47"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="47"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
+      <c r="L67" s="42"/>
+      <c r="M67" s="42"/>
+      <c r="N67" s="42"/>
+      <c r="O67" s="42"/>
+      <c r="P67" s="42"/>
+      <c r="Q67" s="42"/>
+      <c r="R67" s="42"/>
+      <c r="S67" s="42"/>
+      <c r="T67" s="42"/>
+      <c r="U67" s="42"/>
+      <c r="V67" s="42"/>
+      <c r="W67" s="43"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" s="34"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" s="34"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:W49"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A65:W66"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:W14"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:K47"/>
-    <mergeCell ref="L17:W47"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A6:W7"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A10:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
@@ -4179,7 +5339,7 @@
     <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -4220,7 +5380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>65</v>
       </c>
@@ -4267,7 +5427,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
@@ -4293,7 +5453,7 @@
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -4361,7 +5521,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -4420,7 +5580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -4479,7 +5639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -4538,7 +5698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -4597,7 +5757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -4656,7 +5816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -4715,7 +5875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -4774,7 +5934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -4833,7 +5993,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -4901,7 +6061,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H145"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -4913,7 +6073,7 @@
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -4939,7 +6099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3292</v>
       </c>
@@ -4962,7 +6122,7 @@
         <v>45779.458333333001</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3337</v>
       </c>
@@ -4985,7 +6145,7 @@
         <v>45779.465277777999</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3338</v>
       </c>
@@ -5008,7 +6168,7 @@
         <v>45779.479166666999</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3344</v>
       </c>
@@ -5031,7 +6191,7 @@
         <v>45779.458333333001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3345</v>
       </c>
@@ -5054,7 +6214,7 @@
         <v>45780.472222222001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3346</v>
       </c>
@@ -5077,7 +6237,7 @@
         <v>45779.482638889</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4502</v>
       </c>
@@ -5100,7 +6260,7 @@
         <v>45777.452777778002</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4503</v>
       </c>
@@ -5123,7 +6283,7 @@
         <v>45777.457638888998</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4504</v>
       </c>
@@ -5146,7 +6306,7 @@
         <v>45777.462500000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4505</v>
       </c>
@@ -5169,7 +6329,7 @@
         <v>45777.466666667002</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>4506</v>
       </c>
@@ -5192,7 +6352,7 @@
         <v>45777.471527777998</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>4507</v>
       </c>
@@ -5215,7 +6375,7 @@
         <v>45777.476388889001</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4508</v>
       </c>
@@ -5238,7 +6398,7 @@
         <v>45777.481249999997</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>4509</v>
       </c>
@@ -5261,7 +6421,7 @@
         <v>45777.486111111</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>4510</v>
       </c>
@@ -5284,7 +6444,7 @@
         <v>45777.490277778001</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>4511</v>
       </c>
@@ -5307,7 +6467,7 @@
         <v>45777.493750000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>3336</v>
       </c>
@@ -5330,7 +6490,7 @@
         <v>45778.434027777999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>3339</v>
       </c>
@@ -5353,7 +6513,7 @@
         <v>45778.458333333001</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>3340</v>
       </c>
@@ -5376,7 +6536,7 @@
         <v>45778.472916667</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>3353</v>
       </c>
@@ -5399,7 +6559,7 @@
         <v>45778.434027777999</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>3356</v>
       </c>
@@ -5422,7 +6582,7 @@
         <v>45778.447916666999</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>3357</v>
       </c>
@@ -5445,7 +6605,7 @@
         <v>45778.458333333001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>4468</v>
       </c>
@@ -5468,7 +6628,7 @@
         <v>45777.4375</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>4470</v>
       </c>
@@ -5491,7 +6651,7 @@
         <v>45777.441666667</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>4471</v>
       </c>
@@ -5514,7 +6674,7 @@
         <v>45777.445138889001</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>4472</v>
       </c>
@@ -5537,7 +6697,7 @@
         <v>45777.449305556001</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>4473</v>
       </c>
@@ -5560,7 +6720,7 @@
         <v>45777.452777778002</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>4474</v>
       </c>
@@ -5583,7 +6743,7 @@
         <v>45777.456250000003</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>4475</v>
       </c>
@@ -5606,7 +6766,7 @@
         <v>45777.460416667003</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4476</v>
       </c>
@@ -5629,7 +6789,7 @@
         <v>45777.465972222002</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>4477</v>
       </c>
@@ -5652,7 +6812,7 @@
         <v>45777.470833332998</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>4478</v>
       </c>
@@ -5675,7 +6835,7 @@
         <v>45777.474999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>3247</v>
       </c>
@@ -5698,7 +6858,7 @@
         <v>45777.086805555999</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3248</v>
       </c>
@@ -5721,7 +6881,7 @@
         <v>45777.114583333001</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>3249</v>
       </c>
@@ -5744,7 +6904,7 @@
         <v>45777.128472222001</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>3284</v>
       </c>
@@ -5767,7 +6927,7 @@
         <v>45777.586111110999</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>3288</v>
       </c>
@@ -5793,7 +6953,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>3352</v>
       </c>
@@ -5816,7 +6976,7 @@
         <v>45777.617361110999</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>4438</v>
       </c>
@@ -5839,7 +6999,7 @@
         <v>45777.580555556</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>4439</v>
       </c>
@@ -5862,7 +7022,7 @@
         <v>45777.586111110999</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>4440</v>
       </c>
@@ -5885,7 +7045,7 @@
         <v>45777.591666667002</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>4441</v>
       </c>
@@ -5908,7 +7068,7 @@
         <v>45777.596527777998</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4442</v>
       </c>
@@ -5931,7 +7091,7 @@
         <v>45777.602083332997</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4443</v>
       </c>
@@ -5954,7 +7114,7 @@
         <v>45777.606249999997</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4444</v>
       </c>
@@ -5977,7 +7137,7 @@
         <v>45777.611805556</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>4445</v>
       </c>
@@ -6000,7 +7160,7 @@
         <v>45777.615277778001</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>4446</v>
       </c>
@@ -6023,7 +7183,7 @@
         <v>45777.621527777999</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4447</v>
       </c>
@@ -6046,7 +7206,7 @@
         <v>45777.628472222001</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>3341</v>
       </c>
@@ -6069,7 +7229,7 @@
         <v>45778.517361111</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>3342</v>
       </c>
@@ -6092,7 +7252,7 @@
         <v>45778.529166667002</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>3343</v>
       </c>
@@ -6115,7 +7275,7 @@
         <v>45778.055555555999</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>3358</v>
       </c>
@@ -6138,7 +7298,7 @@
         <v>45778.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>3359</v>
       </c>
@@ -6161,7 +7321,7 @@
         <v>45778.513888889</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>3361</v>
       </c>
@@ -6184,7 +7344,7 @@
         <v>45778.527777777999</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>4479</v>
       </c>
@@ -6207,7 +7367,7 @@
         <v>45777.515277778002</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>4480</v>
       </c>
@@ -6230,7 +7390,7 @@
         <v>45777.519444443999</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>4481</v>
       </c>
@@ -6253,7 +7413,7 @@
         <v>45777.522916667003</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>4482</v>
       </c>
@@ -6276,7 +7436,7 @@
         <v>45777.526388888997</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>4483</v>
       </c>
@@ -6299,7 +7459,7 @@
         <v>45777.530555555997</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>4484</v>
       </c>
@@ -6322,7 +7482,7 @@
         <v>45777.534027777998</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>4485</v>
       </c>
@@ -6345,7 +7505,7 @@
         <v>45777.537499999999</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>4486</v>
       </c>
@@ -6368,7 +7528,7 @@
         <v>45777.541666666999</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>4487</v>
       </c>
@@ -6391,7 +7551,7 @@
         <v>45777.546527778002</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>4488</v>
       </c>
@@ -6414,7 +7574,7 @@
         <v>45777.55</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>3333</v>
       </c>
@@ -6437,7 +7597,7 @@
         <v>45779.055555555999</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>3334</v>
       </c>
@@ -6460,7 +7620,7 @@
         <v>45779.056944443997</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>3335</v>
       </c>
@@ -6483,7 +7643,7 @@
         <v>45779.083333333001</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>3348</v>
       </c>
@@ -6506,7 +7666,7 @@
         <v>45778.559027777999</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>3351</v>
       </c>
@@ -6529,7 +7689,7 @@
         <v>45779.572916666999</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>3364</v>
       </c>
@@ -6552,7 +7712,7 @@
         <v>45779.586805555999</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>4512</v>
       </c>
@@ -6575,7 +7735,7 @@
         <v>45777.554166667003</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>4513</v>
       </c>
@@ -6598,7 +7758,7 @@
         <v>45777.560416667002</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>4514</v>
       </c>
@@ -6621,7 +7781,7 @@
         <v>45777.557638888997</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>4515</v>
       </c>
@@ -6644,7 +7804,7 @@
         <v>45777.564583332998</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>4516</v>
       </c>
@@ -6667,7 +7827,7 @@
         <v>45777.567361111003</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>4517</v>
       </c>
@@ -6690,7 +7850,7 @@
         <v>45777.570833332997</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>4518</v>
       </c>
@@ -6713,7 +7873,7 @@
         <v>45777.574305556001</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>4519</v>
       </c>
@@ -6736,7 +7896,7 @@
         <v>45777.577777778002</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>4520</v>
       </c>
@@ -6759,7 +7919,7 @@
         <v>45777.580555556</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>4521</v>
       </c>
@@ -6782,7 +7942,7 @@
         <v>45777.584027778001</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>3261</v>
       </c>
@@ -6805,7 +7965,7 @@
         <v>45777.510416666999</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>3272</v>
       </c>
@@ -6828,7 +7988,7 @@
         <v>45777.509722221999</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>3273</v>
       </c>
@@ -6851,7 +8011,7 @@
         <v>45777.519444443999</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>3279</v>
       </c>
@@ -6874,7 +8034,7 @@
         <v>45777.529166667002</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>3360</v>
       </c>
@@ -6897,7 +8057,7 @@
         <v>45777.522222222004</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>3362</v>
       </c>
@@ -6920,7 +8080,7 @@
         <v>45777.534722222001</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>4428</v>
       </c>
@@ -6943,7 +8103,7 @@
         <v>45777.506249999999</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>4429</v>
       </c>
@@ -6966,7 +8126,7 @@
         <v>45777.511111111002</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>4430</v>
       </c>
@@ -6989,7 +8149,7 @@
         <v>45777.515972221998</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>4431</v>
       </c>
@@ -7012,7 +8172,7 @@
         <v>45777.519444443999</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>4432</v>
       </c>
@@ -7035,7 +8195,7 @@
         <v>45777.522916667003</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>4433</v>
       </c>
@@ -7058,7 +8218,7 @@
         <v>45777.527083333</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>4434</v>
       </c>
@@ -7081,7 +8241,7 @@
         <v>45777.53125</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>4435</v>
       </c>
@@ -7104,7 +8264,7 @@
         <v>45777.536111111003</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>4436</v>
       </c>
@@ -7127,7 +8287,7 @@
         <v>45777.540972221999</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>4437</v>
       </c>
@@ -7150,7 +8310,7 @@
         <v>45777.545833333003</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>3347</v>
       </c>
@@ -7173,7 +8333,7 @@
         <v>45779.378472222001</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>3349</v>
       </c>
@@ -7196,7 +8356,7 @@
         <v>45779.399305555999</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>3350</v>
       </c>
@@ -7219,7 +8379,7 @@
         <v>45779.409722222001</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>3365</v>
       </c>
@@ -7242,7 +8402,7 @@
         <v>45779.375</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>3366</v>
       </c>
@@ -7265,7 +8425,7 @@
         <v>45779.388888889</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>3367</v>
       </c>
@@ -7288,7 +8448,7 @@
         <v>45779.402777777999</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>4492</v>
       </c>
@@ -7311,7 +8471,7 @@
         <v>45777.379166667</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>4493</v>
       </c>
@@ -7334,7 +8494,7 @@
         <v>45777.383333332997</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>4494</v>
       </c>
@@ -7357,7 +8517,7 @@
         <v>45777.388194444</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>4495</v>
       </c>
@@ -7380,7 +8540,7 @@
         <v>45777.392361111</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>4496</v>
       </c>
@@ -7403,7 +8563,7 @@
         <v>45777.396527778001</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>4497</v>
       </c>
@@ -7426,7 +8586,7 @@
         <v>45777.400694443997</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>4498</v>
       </c>
@@ -7449,7 +8609,7 @@
         <v>45777.40625</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>4499</v>
       </c>
@@ -7472,7 +8632,7 @@
         <v>45777.409722222001</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>4500</v>
       </c>
@@ -7495,7 +8655,7 @@
         <v>45777.413888889001</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>4501</v>
       </c>
@@ -7518,7 +8678,7 @@
         <v>45777.417361111002</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>3256</v>
       </c>
@@ -7541,7 +8701,7 @@
         <v>45777.443055556003</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>3259</v>
       </c>
@@ -7564,7 +8724,7 @@
         <v>45777.465277777999</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>3260</v>
       </c>
@@ -7587,7 +8747,7 @@
         <v>45777.481944444</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>3269</v>
       </c>
@@ -7610,7 +8770,7 @@
         <v>45777.399305555999</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>3270</v>
       </c>
@@ -7633,7 +8793,7 @@
         <v>45777.413194444001</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>3271</v>
       </c>
@@ -7656,7 +8816,7 @@
         <v>45777.424305556</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>4404</v>
       </c>
@@ -7679,7 +8839,7 @@
         <v>45777.390277778002</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>4405</v>
       </c>
@@ -7702,7 +8862,7 @@
         <v>45777.395138888998</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>4406</v>
       </c>
@@ -7725,7 +8885,7 @@
         <v>45777.402083333</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>4408</v>
       </c>
@@ -7748,7 +8908,7 @@
         <v>45777.409027777998</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>4409</v>
       </c>
@@ -7771,7 +8931,7 @@
         <v>45777.415972221999</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>4411</v>
       </c>
@@ -7794,7 +8954,7 @@
         <v>45777.419444444</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>4414</v>
       </c>
@@ -7817,7 +8977,7 @@
         <v>45777.423611111</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>4417</v>
       </c>
@@ -7840,7 +9000,7 @@
         <v>45777.423611111</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>4426</v>
       </c>
@@ -7863,7 +9023,7 @@
         <v>45777.432638888997</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>4427</v>
       </c>
@@ -7886,7 +9046,7 @@
         <v>45777.436111110997</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>3140</v>
       </c>
@@ -7909,7 +9069,7 @@
         <v>45771.447916666999</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>3141</v>
       </c>
@@ -7932,7 +9092,7 @@
         <v>45771.458333333001</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>3143</v>
       </c>
@@ -7955,7 +9115,7 @@
         <v>45771.46875</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>3144</v>
       </c>
@@ -7978,7 +9138,7 @@
         <v>45771.479166666999</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>3145</v>
       </c>
@@ -8001,7 +9161,7 @@
         <v>45771.489583333001</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>3146</v>
       </c>
@@ -8024,7 +9184,7 @@
         <v>45771.5</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>4375</v>
       </c>
@@ -8047,7 +9207,7 @@
         <v>45771.420138889</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>4376</v>
       </c>
@@ -8070,7 +9230,7 @@
         <v>45771.427083333001</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>4377</v>
       </c>
@@ -8093,7 +9253,7 @@
         <v>45771.432638888997</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>4378</v>
       </c>
@@ -8116,7 +9276,7 @@
         <v>45771.439583332998</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>4379</v>
       </c>
@@ -8139,7 +9299,7 @@
         <v>45771.446527777996</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>4380</v>
       </c>
@@ -8162,7 +9322,7 @@
         <v>45771.453472221998</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>4381</v>
       </c>
@@ -8185,7 +9345,7 @@
         <v>45771.459722222004</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>4382</v>
       </c>
@@ -8208,7 +9368,7 @@
         <v>45761.467361110997</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>4383</v>
       </c>
@@ -8231,7 +9391,7 @@
         <v>45771.472222222001</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>4384</v>
       </c>
@@ -8263,14 +9423,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -8281,7 +9441,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2</v>
       </c>
@@ -8292,7 +9452,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -8303,7 +9463,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5</v>
       </c>
@@ -8314,7 +9474,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>8</v>
       </c>
@@ -8325,7 +9485,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7</v>
       </c>
@@ -8336,7 +9496,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>10</v>
       </c>
@@ -8347,7 +9507,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>9</v>
       </c>
@@ -8358,7 +9518,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>12</v>
       </c>
@@ -8369,7 +9529,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>14</v>
       </c>
@@ -8380,7 +9540,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>15</v>
       </c>
@@ -8391,7 +9551,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>16</v>
       </c>
@@ -8402,7 +9562,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>17</v>
       </c>
@@ -8413,7 +9573,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>18</v>
       </c>
@@ -8433,7 +9593,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
@@ -8442,7 +9602,7 @@
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -8459,7 +9619,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8470,7 +9630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8481,7 +9641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5</v>
       </c>
@@ -8492,7 +9652,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>6</v>
       </c>
@@ -8503,7 +9663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7</v>
       </c>
@@ -8517,7 +9677,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>12</v>
       </c>
@@ -8528,7 +9688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>13</v>
       </c>
@@ -8539,7 +9699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>14</v>
       </c>
@@ -8550,7 +9710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>15</v>
       </c>
@@ -8561,7 +9721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>17</v>
       </c>
@@ -8572,7 +9732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20</v>
       </c>
@@ -8583,7 +9743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>21</v>
       </c>
@@ -8594,7 +9754,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>29</v>
       </c>
@@ -8605,7 +9765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>32</v>
       </c>
@@ -8616,7 +9776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>46</v>
       </c>
@@ -8627,7 +9787,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>48</v>
       </c>
@@ -8638,7 +9798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>50</v>
       </c>
@@ -8649,7 +9809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>51</v>
       </c>
@@ -8660,7 +9820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>55</v>
       </c>
@@ -8671,7 +9831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>60</v>
       </c>
@@ -8682,7 +9842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>64</v>
       </c>
@@ -8693,7 +9853,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>66</v>
       </c>
@@ -8704,7 +9864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>70</v>
       </c>
@@ -8715,7 +9875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>71</v>
       </c>
@@ -8726,7 +9886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>73</v>
       </c>
@@ -8737,7 +9897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>77</v>
       </c>
@@ -8748,7 +9908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>81</v>
       </c>
@@ -8759,7 +9919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>82</v>
       </c>
@@ -8770,7 +9930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>84</v>
       </c>
@@ -8781,7 +9941,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>85</v>
       </c>
@@ -8792,7 +9952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>86</v>
       </c>
@@ -8803,7 +9963,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>99</v>
       </c>
@@ -8817,7 +9977,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>121</v>
       </c>
@@ -8831,7 +9991,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>133</v>
       </c>
@@ -8842,7 +10002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>134</v>
       </c>
@@ -8853,7 +10013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>135</v>
       </c>
@@ -8864,7 +10024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>136</v>
       </c>
@@ -8875,7 +10035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>137</v>
       </c>
@@ -8886,7 +10046,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>140</v>
       </c>
@@ -8900,7 +10060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>142</v>
       </c>
@@ -8914,7 +10074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>149</v>
       </c>
@@ -8928,7 +10088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>151</v>
       </c>
@@ -8942,7 +10102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>155</v>
       </c>
@@ -8956,7 +10116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>158</v>
       </c>
@@ -8970,7 +10130,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>173</v>
       </c>
@@ -8984,7 +10144,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>177</v>
       </c>
@@ -8998,7 +10158,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>188</v>
       </c>
@@ -9012,7 +10172,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>189</v>
       </c>
@@ -9026,7 +10186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>190</v>
       </c>
@@ -9040,7 +10200,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>192</v>
       </c>
@@ -9054,7 +10214,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>195</v>
       </c>
@@ -9068,7 +10228,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>196</v>
       </c>
@@ -9082,7 +10242,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>200</v>
       </c>
@@ -9096,7 +10256,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>206</v>
       </c>
@@ -9110,7 +10270,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>207</v>
       </c>
@@ -9124,7 +10284,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>213</v>
       </c>
@@ -9138,7 +10298,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>371</v>
       </c>
@@ -9155,7 +10315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>445</v>
       </c>
@@ -9181,7 +10341,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
@@ -9189,7 +10349,7 @@
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -9206,7 +10366,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3</v>
       </c>
@@ -9223,7 +10383,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>5</v>
       </c>
@@ -9240,7 +10400,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>12</v>
       </c>
@@ -9254,7 +10414,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>14</v>
       </c>
@@ -9271,7 +10431,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>18</v>
       </c>
@@ -9288,7 +10448,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>21</v>
       </c>
@@ -9305,7 +10465,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>36</v>
       </c>
@@ -9322,7 +10482,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>40</v>
       </c>
@@ -9336,7 +10496,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>51</v>
       </c>
@@ -9353,7 +10513,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>52</v>
       </c>
@@ -9370,7 +10530,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>53</v>
       </c>
@@ -9387,7 +10547,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>55</v>
       </c>
@@ -9404,7 +10564,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>58</v>
       </c>
@@ -9421,7 +10581,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>59</v>
       </c>
@@ -9438,7 +10598,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>63</v>
       </c>
@@ -9455,7 +10615,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>69</v>
       </c>
@@ -9472,7 +10632,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>70</v>
       </c>
@@ -9489,7 +10649,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>76</v>
       </c>
@@ -9506,7 +10666,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>99</v>
       </c>
@@ -9529,7 +10689,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
@@ -9538,15 +10698,15 @@
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.28515625" customWidth="1"/>
+    <col min="9" max="9" width="2.26953125" customWidth="1"/>
     <col min="10" max="10" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.28515625" customWidth="1"/>
+    <col min="13" max="13" width="2.26953125" customWidth="1"/>
     <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9564,7 +10724,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -9604,7 +10764,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -9639,7 +10799,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -9674,7 +10834,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -9709,7 +10869,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>6</v>
       </c>
@@ -9744,7 +10904,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>8</v>
       </c>
@@ -9779,7 +10939,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>10</v>
       </c>
@@ -9814,7 +10974,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>13</v>
       </c>
@@ -9849,7 +11009,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>17</v>
       </c>
@@ -9884,7 +11044,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>18</v>
       </c>
@@ -9919,7 +11079,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20</v>
       </c>
@@ -9954,7 +11114,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>35</v>
       </c>
@@ -9989,7 +11149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>36</v>
       </c>
@@ -10024,7 +11184,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>37</v>
       </c>
@@ -10059,7 +11219,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>38</v>
       </c>
@@ -10094,7 +11254,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>42</v>
       </c>
@@ -10129,7 +11289,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>43</v>
       </c>
@@ -10164,7 +11324,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>46</v>
       </c>
@@ -10196,7 +11356,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>47</v>
       </c>
@@ -10231,7 +11391,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>48</v>
       </c>
@@ -10266,7 +11426,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>49</v>
       </c>
@@ -10301,7 +11461,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>50</v>
       </c>
@@ -10336,7 +11496,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>53</v>
       </c>
@@ -10371,7 +11531,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>56</v>
       </c>
@@ -10406,7 +11566,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>58</v>
       </c>
@@ -10441,7 +11601,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>60</v>
       </c>
@@ -10476,7 +11636,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>63</v>
       </c>
@@ -10511,7 +11671,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>68</v>
       </c>
@@ -10546,7 +11706,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>75</v>
       </c>
@@ -10581,7 +11741,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>76</v>
       </c>
@@ -10616,7 +11776,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>82</v>
       </c>
@@ -10654,7 +11814,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>83</v>
       </c>
@@ -10692,7 +11852,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>84</v>
       </c>
@@ -10730,7 +11890,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>85</v>
       </c>
@@ -10768,7 +11928,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>86</v>
       </c>
@@ -10806,7 +11966,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>87</v>
       </c>
@@ -10844,7 +12004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>88</v>
       </c>
@@ -10882,7 +12042,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>89</v>
       </c>
@@ -10920,7 +12080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>90</v>
       </c>
@@ -10958,7 +12118,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>91</v>
       </c>
@@ -10993,7 +12153,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>103</v>
       </c>
@@ -11022,7 +12182,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>114</v>
       </c>
@@ -11054,7 +12214,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>122</v>
       </c>
@@ -11092,7 +12252,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>123</v>
       </c>
@@ -11130,7 +12290,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>124</v>
       </c>
@@ -11168,7 +12328,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>125</v>
       </c>
@@ -11206,7 +12366,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>126</v>
       </c>
@@ -11244,7 +12404,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>127</v>
       </c>
@@ -11282,7 +12442,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>130</v>
       </c>
